--- a/Akasi/Backend/massCreateExcel.xlsx
+++ b/Akasi/Backend/massCreateExcel.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Baste\Research\GitRepos\EVC-AKASI\Akasi\Frontend\components\manager\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\TRANSFER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D614C06-1A43-44AD-B78B-2283B565BBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262C1407-AEB8-414F-AE6F-6C6729E310C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{A1CD2441-050B-4C0D-8089-C93FF557E34F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A1CD2441-050B-4C0D-8089-C93FF557E34F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -470,13 +470,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC19F18-1592-4798-BD30-FF012EFC0E76}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.73046875" customWidth="1"/>
-    <col min="4" max="4" width="16.796875" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
